--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55113915</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106986</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55115506</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55105716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55107209</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106371</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106547</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55107091</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55107169</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55113854</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106277</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1927,6 +1987,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106709</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106943</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55113934</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2239,6 +2314,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55115565</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2343,6 +2423,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106476</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2447,6 +2532,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55113814</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2551,6 +2641,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55115501</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2655,6 +2750,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55107076</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2759,6 +2859,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55113875</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2863,6 +2968,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55107351</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2967,6 +3077,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55107395</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3071,6 +3186,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55115226</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3175,6 +3295,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55105732</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3279,6 +3404,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106658</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3383,6 +3513,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106951</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3487,6 +3622,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55113938</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3591,6 +3731,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55136036</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3695,6 +3840,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55105738</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3799,6 +3949,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106402</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3903,6 +4058,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106979</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4007,6 +4167,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55113944</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4111,6 +4276,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106671</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4215,6 +4385,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106907</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4319,6 +4494,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55115570</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4423,6 +4603,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106718</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4527,6 +4712,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106965</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4631,6 +4821,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55115563</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4742,6 +4937,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55107177</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4847,6 +5047,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106245</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4952,6 +5157,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106282</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5057,6 +5267,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106258</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5161,8 +5376,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55115505</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ44"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,47 +1007,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55105716</v>
+        <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>96164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1131</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Asphättemossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nyholmiella gymnostoma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bruch ex Brid.) Holmen &amp; Warncke</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kardiberget, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>728165</v>
+        <v>727966</v>
       </c>
       <c r="R5" t="n">
-        <v>7367461</v>
+        <v>7367594</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1074,17 +1075,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På grov granlåga. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal asp. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1094,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,13 +1111,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55105716</t>
+          <t>https://artportalen.se/Sighting/55107358</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55107209</v>
+        <v>55105716</v>
       </c>
       <c r="B6" t="n">
         <v>91909</v>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>728050</v>
+        <v>728165</v>
       </c>
       <c r="R6" t="n">
-        <v>7367558</v>
+        <v>7367461</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granlåga. 6 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På grov granlåga. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,38 +1221,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55107209</t>
+          <t>https://artportalen.se/Sighting/55105716</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55106371</v>
+        <v>55107209</v>
       </c>
       <c r="B7" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>728145</v>
+        <v>728050</v>
       </c>
       <c r="R7" t="n">
-        <v>7367471</v>
+        <v>7367558</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal granlåga. En observation inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På granlåga. 6 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,38 +1331,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106371</t>
+          <t>https://artportalen.se/Sighting/55107209</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>55106547</v>
+        <v>55106371</v>
       </c>
       <c r="B8" t="n">
-        <v>83173</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>728108</v>
+        <v>728145</v>
       </c>
       <c r="R8" t="n">
-        <v>7367504</v>
+        <v>7367471</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>36 observationer på gamla granar inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal granlåga. En observation inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,13 +1441,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106547</t>
+          <t>https://artportalen.se/Sighting/55106371</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55107091</v>
+        <v>55106547</v>
       </c>
       <c r="B9" t="n">
         <v>83173</v>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>728081</v>
+        <v>728108</v>
       </c>
       <c r="R9" t="n">
-        <v>7367514</v>
+        <v>7367504</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>36 observationer av gammelgransskål på gamla granar inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>36 observationer på gamla granar inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,19 +1545,19 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55107091</t>
+          <t>https://artportalen.se/Sighting/55106547</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55107169</v>
+        <v>55107091</v>
       </c>
       <c r="B10" t="n">
         <v>83173</v>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>728059</v>
+        <v>728081</v>
       </c>
       <c r="R10" t="n">
-        <v>7367550</v>
+        <v>7367514</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>36 observationer av gammelgransskål på gamla granar inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,13 +1661,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55107169</t>
+          <t>https://artportalen.se/Sighting/55107091</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55113854</v>
+        <v>55107169</v>
       </c>
       <c r="B11" t="n">
         <v>83173</v>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>728133</v>
+        <v>728059</v>
       </c>
       <c r="R11" t="n">
-        <v>7367465</v>
+        <v>7367550</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>36 observationer av gammelgransskål inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,22 +1765,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55113854</t>
+          <t>https://artportalen.se/Sighting/55107169</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>55106277</v>
+        <v>55113854</v>
       </c>
       <c r="B12" t="n">
-        <v>80433</v>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>727941</v>
+        <v>728133</v>
       </c>
       <c r="R12" t="n">
-        <v>7367605</v>
+        <v>7367465</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1844,17 +1844,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal sälg. 14 observationer av skrovellav inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>36 observationer av gammelgransskål inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,6 +1863,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1880,13 +1881,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106277</t>
+          <t>https://artportalen.se/Sighting/55113854</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>55106709</v>
+        <v>55106277</v>
       </c>
       <c r="B13" t="n">
         <v>80433</v>
@@ -1923,10 +1924,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>728113</v>
+        <v>727941</v>
       </c>
       <c r="R13" t="n">
-        <v>7367505</v>
+        <v>7367605</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1953,17 +1954,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg. 14 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. 14 observationer av skrovellav inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,13 +1990,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106709</t>
+          <t>https://artportalen.se/Sighting/55106277</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55106943</v>
+        <v>55106709</v>
       </c>
       <c r="B14" t="n">
         <v>80433</v>
@@ -2032,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>728100</v>
+        <v>728113</v>
       </c>
       <c r="R14" t="n">
-        <v>7367525</v>
+        <v>7367505</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2098,13 +2099,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106943</t>
+          <t>https://artportalen.se/Sighting/55106709</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>55113934</v>
+        <v>55106943</v>
       </c>
       <c r="B15" t="n">
         <v>80433</v>
@@ -2141,10 +2142,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>728114</v>
+        <v>728100</v>
       </c>
       <c r="R15" t="n">
-        <v>7367484</v>
+        <v>7367525</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2181,7 +2182,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal sälg. 14 observationer inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. 14 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,13 +2208,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55113934</t>
+          <t>https://artportalen.se/Sighting/55106943</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55115565</v>
+        <v>55113934</v>
       </c>
       <c r="B16" t="n">
         <v>80433</v>
@@ -2250,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>727946</v>
+        <v>728114</v>
       </c>
       <c r="R16" t="n">
-        <v>7367613</v>
+        <v>7367484</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2290,7 +2291,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal sälg. 14 fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. 14 observationer inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,38 +2317,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55115565</t>
+          <t>https://artportalen.se/Sighting/55113934</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55106476</v>
+        <v>55115565</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2359,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728134</v>
+        <v>727946</v>
       </c>
       <c r="R17" t="n">
-        <v>7367476</v>
+        <v>7367613</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2399,7 +2400,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Finns allmänt förekommande. Över 50 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. 14 fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2425,13 +2426,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106476</t>
+          <t>https://artportalen.se/Sighting/55115565</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>55113814</v>
+        <v>55106476</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2468,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>728133</v>
+        <v>728134</v>
       </c>
       <c r="R18" t="n">
-        <v>7367465</v>
+        <v>7367476</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2508,7 +2509,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fertil garnlav på gammal gran. Över 50 observationer av garnlav inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>Finns allmänt förekommande. Över 50 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,38 +2535,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55113814</t>
+          <t>https://artportalen.se/Sighting/55106476</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>55115501</v>
+        <v>55113814</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2577,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>727952</v>
+        <v>728133</v>
       </c>
       <c r="R19" t="n">
-        <v>7367608</v>
+        <v>7367465</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2617,7 +2618,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ett fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>Fertil garnlav på gammal gran. Över 50 observationer av garnlav inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,16 +2644,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55115501</t>
+          <t>https://artportalen.se/Sighting/55113814</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55107076</v>
+        <v>55115501</v>
       </c>
       <c r="B20" t="n">
-        <v>83307</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,21 +2661,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2686,10 +2687,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>728081</v>
+        <v>727952</v>
       </c>
       <c r="R20" t="n">
-        <v>7367514</v>
+        <v>7367608</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2726,7 +2727,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>35 observationer av vitgrynig nållav på gamla granar inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>Ett fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,13 +2753,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55107076</t>
+          <t>https://artportalen.se/Sighting/55115501</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>55113875</v>
+        <v>55107076</v>
       </c>
       <c r="B21" t="n">
         <v>83307</v>
@@ -2795,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>728133</v>
+        <v>728081</v>
       </c>
       <c r="R21" t="n">
-        <v>7367465</v>
+        <v>7367514</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2835,7 +2836,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>35 observationer av vitgrynig nållav på gamla granar inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>35 observationer av vitgrynig nållav på gamla granar inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2861,38 +2862,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55113875</t>
+          <t>https://artportalen.se/Sighting/55107076</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>55107351</v>
+        <v>55113875</v>
       </c>
       <c r="B22" t="n">
-        <v>80336</v>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2904,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>727966</v>
+        <v>728133</v>
       </c>
       <c r="R22" t="n">
-        <v>7367594</v>
+        <v>7367465</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2944,7 +2945,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal asp. 19 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>35 observationer av vitgrynig nållav på gamla granar inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2970,13 +2971,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55107351</t>
+          <t>https://artportalen.se/Sighting/55113875</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>55107395</v>
+        <v>55107351</v>
       </c>
       <c r="B23" t="n">
         <v>80336</v>
@@ -3013,10 +3014,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>727957</v>
+        <v>727966</v>
       </c>
       <c r="R23" t="n">
-        <v>7367606</v>
+        <v>7367594</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3053,7 +3054,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal asp. 19 fynd inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal asp. 19 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3079,13 +3080,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55107395</t>
+          <t>https://artportalen.se/Sighting/55107351</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>55115226</v>
+        <v>55107395</v>
       </c>
       <c r="B24" t="n">
         <v>80336</v>
@@ -3122,10 +3123,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>727966</v>
+        <v>727957</v>
       </c>
       <c r="R24" t="n">
-        <v>7367584</v>
+        <v>7367606</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3162,7 +3163,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal asp. 19 fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal asp. 19 fynd inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,38 +3189,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55115226</t>
+          <t>https://artportalen.se/Sighting/55107395</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55105732</v>
+        <v>55115226</v>
       </c>
       <c r="B25" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3231,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>728149</v>
+        <v>727966</v>
       </c>
       <c r="R25" t="n">
-        <v>7367455</v>
+        <v>7367584</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3261,17 +3262,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal sälg. 55 observationer av lunglav inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal asp. 19 fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3297,13 +3298,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55105732</t>
+          <t>https://artportalen.se/Sighting/55115226</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>55106658</v>
+        <v>55105732</v>
       </c>
       <c r="B26" t="n">
         <v>80432</v>
@@ -3340,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>728101</v>
+        <v>728149</v>
       </c>
       <c r="R26" t="n">
-        <v>7367501</v>
+        <v>7367455</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3370,17 +3371,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sälglåga. 55 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. 55 observationer av lunglav inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3406,13 +3407,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106658</t>
+          <t>https://artportalen.se/Sighting/55105732</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>55106951</v>
+        <v>55106658</v>
       </c>
       <c r="B27" t="n">
         <v>80432</v>
@@ -3449,10 +3450,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>728100</v>
+        <v>728101</v>
       </c>
       <c r="R27" t="n">
-        <v>7367525</v>
+        <v>7367501</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3489,7 +3490,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal sälg. 55 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På sälglåga. 55 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3515,13 +3516,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106951</t>
+          <t>https://artportalen.se/Sighting/55106658</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>55113938</v>
+        <v>55106951</v>
       </c>
       <c r="B28" t="n">
         <v>80432</v>
@@ -3558,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>728114</v>
+        <v>728100</v>
       </c>
       <c r="R28" t="n">
-        <v>7367484</v>
+        <v>7367525</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3598,7 +3599,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal sälg. 55 fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. 55 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3624,13 +3625,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55113938</t>
+          <t>https://artportalen.se/Sighting/55106951</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>55136036</v>
+        <v>55113938</v>
       </c>
       <c r="B29" t="n">
         <v>80432</v>
@@ -3667,10 +3668,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>727821</v>
+        <v>728114</v>
       </c>
       <c r="R29" t="n">
-        <v>7367495</v>
+        <v>7367484</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,17 +3698,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2015-08-27</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2015-08-27</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på grov sälg utanför provytan.</t>
+          <t>På gammal sälg. 55 fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,38 +3734,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55136036</t>
+          <t>https://artportalen.se/Sighting/55113938</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>55105738</v>
+        <v>55136036</v>
       </c>
       <c r="B30" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3776,10 +3777,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>728149</v>
+        <v>727821</v>
       </c>
       <c r="R30" t="n">
-        <v>7367455</v>
+        <v>7367495</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3806,17 +3807,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-27</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal sälg. Över 50 observationer av stuplav inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>Rikligt med lunglav på grov sälg utanför provytan.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,13 +3843,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55105738</t>
+          <t>https://artportalen.se/Sighting/55136036</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>55106402</v>
+        <v>55105738</v>
       </c>
       <c r="B31" t="n">
         <v>80461</v>
@@ -3885,10 +3886,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>728134</v>
+        <v>728149</v>
       </c>
       <c r="R31" t="n">
-        <v>7367476</v>
+        <v>7367455</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3915,17 +3916,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På enbuske. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. Över 50 observationer av stuplav inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3951,13 +3952,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106402</t>
+          <t>https://artportalen.se/Sighting/55105738</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>55106979</v>
+        <v>55106402</v>
       </c>
       <c r="B32" t="n">
         <v>80461</v>
@@ -3994,10 +3995,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>728100</v>
+        <v>728134</v>
       </c>
       <c r="R32" t="n">
-        <v>7367525</v>
+        <v>7367476</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4034,7 +4035,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal sälg. Över 50 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På enbuske. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,13 +4061,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106979</t>
+          <t>https://artportalen.se/Sighting/55106402</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>55113944</v>
+        <v>55106979</v>
       </c>
       <c r="B33" t="n">
         <v>80461</v>
@@ -4103,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>728114</v>
+        <v>728100</v>
       </c>
       <c r="R33" t="n">
-        <v>7367484</v>
+        <v>7367525</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4143,7 +4144,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal sälg. Över 50 observationer inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. Över 50 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4169,16 +4170,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55113944</t>
+          <t>https://artportalen.se/Sighting/55106979</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>55106671</v>
+        <v>55113944</v>
       </c>
       <c r="B34" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4186,21 +4187,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4212,10 +4213,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>728101</v>
+        <v>728114</v>
       </c>
       <c r="R34" t="n">
-        <v>7367501</v>
+        <v>7367484</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4252,7 +4253,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Sälglåga. 58 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. Över 50 observationer inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4278,13 +4279,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106671</t>
+          <t>https://artportalen.se/Sighting/55113944</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>55106907</v>
+        <v>55106671</v>
       </c>
       <c r="B35" t="n">
         <v>80467</v>
@@ -4321,10 +4322,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>728113</v>
+        <v>728101</v>
       </c>
       <c r="R35" t="n">
-        <v>7367505</v>
+        <v>7367501</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4361,7 +4362,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal grov sälg. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>Sälglåga. 58 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4387,13 +4388,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106907</t>
+          <t>https://artportalen.se/Sighting/55106671</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>55115570</v>
+        <v>55106907</v>
       </c>
       <c r="B36" t="n">
         <v>80467</v>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>727946</v>
+        <v>728113</v>
       </c>
       <c r="R36" t="n">
-        <v>7367613</v>
+        <v>7367505</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4470,7 +4471,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal sälg. 58 fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal grov sälg. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4496,16 +4497,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55115570</t>
+          <t>https://artportalen.se/Sighting/55106907</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>55106718</v>
+        <v>55115570</v>
       </c>
       <c r="B37" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4513,21 +4514,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4539,10 +4540,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>728113</v>
+        <v>727946</v>
       </c>
       <c r="R37" t="n">
-        <v>7367505</v>
+        <v>7367613</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4579,7 +4580,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal sälg. 30 obsevationer av luddlav inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. 58 fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4605,13 +4606,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106718</t>
+          <t>https://artportalen.se/Sighting/55115570</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>55106965</v>
+        <v>55106718</v>
       </c>
       <c r="B38" t="n">
         <v>80468</v>
@@ -4648,10 +4649,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>728100</v>
+        <v>728113</v>
       </c>
       <c r="R38" t="n">
-        <v>7367525</v>
+        <v>7367505</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4688,7 +4689,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal sälg. 30 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. 30 obsevationer av luddlav inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4714,38 +4715,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106965</t>
+          <t>https://artportalen.se/Sighting/55106718</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>55115563</v>
+        <v>55106965</v>
       </c>
       <c r="B39" t="n">
-        <v>78334</v>
+        <v>80468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4757,10 +4758,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>727946</v>
+        <v>728100</v>
       </c>
       <c r="R39" t="n">
-        <v>7367613</v>
+        <v>7367525</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4797,7 +4798,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På grov tallhögstubbe. Ett fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På gammal sälg. 30 observationer inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4823,60 +4824,53 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55115563</t>
+          <t>https://artportalen.se/Sighting/55106965</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>55107177</v>
+        <v>55115563</v>
       </c>
       <c r="B40" t="n">
-        <v>4781</v>
+        <v>78334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kardiberget, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>728059</v>
+        <v>727946</v>
       </c>
       <c r="R40" t="n">
-        <v>7367550</v>
+        <v>7367613</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,7 +4907,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Kläckhål i barken på gammal gran.Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>På grov tallhögstubbe. Ett fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4933,22 +4927,22 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55107177</t>
+          <t>https://artportalen.se/Sighting/55115563</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>55106245</v>
+        <v>55107177</v>
       </c>
       <c r="B41" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,37 +4950,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kardiberget, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>727933</v>
+        <v>728059</v>
       </c>
       <c r="R41" t="n">
-        <v>7367424</v>
+        <v>7367550</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5013,17 +5013,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Vid vägdike.</t>
+          <t>Kläckhål i barken på gammal gran.Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5043,22 +5043,22 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106245</t>
+          <t>https://artportalen.se/Sighting/55107177</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>55106282</v>
+        <v>55106245</v>
       </c>
       <c r="B42" t="n">
-        <v>97989</v>
+        <v>99035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>727941</v>
+        <v>727933</v>
       </c>
       <c r="R42" t="n">
-        <v>7367605</v>
+        <v>7367424</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Förekommer sparsamt här och där inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>Vid vägdike.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5159,16 +5159,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106282</t>
+          <t>https://artportalen.se/Sighting/55106245</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>55106258</v>
+        <v>55106282</v>
       </c>
       <c r="B43" t="n">
-        <v>97986</v>
+        <v>97989</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5176,16 +5176,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>727916</v>
+        <v>727941</v>
       </c>
       <c r="R43" t="n">
-        <v>7367431</v>
+        <v>7367605</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Vägkant.</t>
+          <t>Förekommer sparsamt här och där inom provytan. Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5269,53 +5269,54 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55106258</t>
+          <t>https://artportalen.se/Sighting/55106282</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>55115505</v>
+        <v>55106258</v>
       </c>
       <c r="B44" t="n">
-        <v>79917</v>
+        <v>97986</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>221946</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kardiberget, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>727952</v>
+        <v>727916</v>
       </c>
       <c r="R44" t="n">
-        <v>7367608</v>
+        <v>7367431</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5342,17 +5343,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ett fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+          <t>Vägkant.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5377,6 +5378,115 @@
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55106258</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>55115505</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kardiberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>727952</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7367608</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2015-08-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2015-08-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ett fynd inom provytan.  Utlottad nyckelbiotop som ingår i Skogsstyrelsens projekt Uppföljning av biologisk mångfald. 50 observerade signal- och rödlistade arter inom provytan, varav 32 rödlistade. Provytans areal är 1,79 ha. Sydsluttning med gammal naturskogsartad barrskog med inslag av gammal sälg och asp.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/55115505</t>
         </is>
@@ -5427,6 +5537,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96164</v>
+        <v>96165</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96165</v>
+        <v>96166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96166</v>
+        <v>96172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96172</v>
+        <v>96173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96173</v>
+        <v>96184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96184</v>
+        <v>96197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96197</v>
+        <v>96198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>96211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96211</v>
+        <v>96212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
